--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,243 +656,255 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2596000</v>
+        <v>939000</v>
       </c>
       <c r="E8" s="3">
-        <v>421000</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+        <v>2561000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>464000</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3">
-        <v>2903000</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I8" s="3">
-        <v>6623000</v>
+        <v>2928000</v>
       </c>
       <c r="J8" s="3">
+        <v>6731000</v>
+      </c>
+      <c r="K8" s="3">
         <v>2209000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1738000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1548000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>259500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5382200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>659600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>184100</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3">
         <v>4935200</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E9" s="3">
         <v>155000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>164000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>172000</v>
       </c>
-      <c r="G9" s="3">
-        <v>-665000</v>
-      </c>
       <c r="H9" s="3">
+        <v>165000</v>
+      </c>
+      <c r="I9" s="3">
         <v>160000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>135000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>137000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>-232000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>-188000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-464700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>612600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>-504400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>-584300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>-876200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>838900</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2441000</v>
+        <v>789000</v>
       </c>
       <c r="E10" s="3">
-        <v>257000</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+        <v>2406000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>300000</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="3">
-        <v>2743000</v>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I10" s="3">
-        <v>6488000</v>
+        <v>2768000</v>
       </c>
       <c r="J10" s="3">
+        <v>6596000</v>
+      </c>
+      <c r="K10" s="3">
         <v>2072000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1970000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1736000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>724200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4769600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1164000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>768400</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3">
         <v>4096300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -912,8 +924,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -965,8 +978,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1018,8 +1034,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1071,8 +1090,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1124,8 +1146,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1142,114 +1167,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2812000</v>
+      </c>
+      <c r="E17" s="3">
         <v>-945000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>-1113000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1262000</v>
       </c>
-      <c r="G17" s="3">
-        <v>532000</v>
-      </c>
       <c r="H17" s="3">
+        <v>-511000</v>
+      </c>
+      <c r="I17" s="3">
         <v>408000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2531000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-412000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>959000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1317000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>763700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1915500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>756600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>635200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1255700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2961300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3541000</v>
+        <v>-1873000</v>
       </c>
       <c r="E18" s="3">
-        <v>1534000</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
+        <v>3506000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1577000</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="3">
-        <v>2495000</v>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I18" s="3">
-        <v>4092000</v>
+        <v>2520000</v>
       </c>
       <c r="J18" s="3">
+        <v>4200000</v>
+      </c>
+      <c r="K18" s="3">
         <v>2621000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>779000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>231000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-504200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3466700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-97000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-451100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>1973900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1269,91 +1301,95 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>10000</v>
+        <v>-47000</v>
       </c>
       <c r="E20" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+        <v>45000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-54000</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
-        <v>59000</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
-        <v>71000</v>
+        <v>34000</v>
       </c>
       <c r="J20" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="K20" s="3">
         <v>12000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-13000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>27000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-27600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>124800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-58800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>-108000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1920000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3551000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1523000</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3">
         <v>2554000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4163000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2633000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>766000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1375,167 +1411,179 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E22" s="3">
         <v>49000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>58000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>43000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>40000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>31400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>41800</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1955000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3502000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1465000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-953000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-1543000</v>
+      </c>
+      <c r="I23" s="3">
         <v>2525000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4139000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2613000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>748000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>252000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-538400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3585400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-163200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-531900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1824100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-395000</v>
+      </c>
+      <c r="E24" s="3">
         <v>712000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>245000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-558000</v>
       </c>
-      <c r="G24" s="3">
-        <v>-235000</v>
-      </c>
       <c r="H24" s="3">
+        <v>-385000</v>
+      </c>
+      <c r="I24" s="3">
         <v>657000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>845000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>388000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>87000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-54500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>585600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-273100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-457000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>33200</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1587,114 +1635,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1560000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2790000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1220000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-718000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-1158000</v>
+      </c>
+      <c r="I26" s="3">
         <v>1868000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3294000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2225000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>661000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>268000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-483900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2999800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>109900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-374900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1790900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1570000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2762000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1204000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-710000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-1150000</v>
+      </c>
+      <c r="I27" s="3">
         <v>1879000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3263000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2194000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>585000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>206000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-540000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2931500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>75700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-396600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1796700</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1746,8 +1803,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1799,8 +1859,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1852,8 +1915,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1905,114 +1971,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-10000</v>
+        <v>47000</v>
       </c>
       <c r="E32" s="3">
-        <v>11000</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+        <v>-45000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>54000</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
-        <v>-59000</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
-        <v>-71000</v>
+        <v>-34000</v>
       </c>
       <c r="J32" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-12000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>13000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-27000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>27600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-124800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>58800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>73000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>108000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1570000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2762000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1204000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-710000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-1150000</v>
+      </c>
+      <c r="I33" s="3">
         <v>1879000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3263000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2194000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>585000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>206000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-540000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2931500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>75700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-396600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1796700</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2064,119 +2139,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1570000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2762000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1204000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-710000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-1150000</v>
+      </c>
+      <c r="I35" s="3">
         <v>1879000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3263000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2194000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>585000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>206000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-540000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2931500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>75700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-396600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1796700</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2196,8 +2280,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2217,47 +2302,48 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2688000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2760000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2100000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1779000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4298000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5331000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5258000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2674000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2623000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2481800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1534600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1572600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2270,8 +2356,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2323,8 +2412,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2376,8 +2468,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2429,8 +2524,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2482,8 +2580,11 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2535,47 +2636,50 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>60198000</v>
+        <v>67351000</v>
       </c>
       <c r="E47" s="3">
-        <v>63337000</v>
+        <v>67180000</v>
       </c>
       <c r="F47" s="3">
-        <v>65834000</v>
+        <v>69488000</v>
       </c>
       <c r="G47" s="3">
-        <v>64676000</v>
+        <v>71276000</v>
       </c>
       <c r="H47" s="3">
+        <v>69762000</v>
+      </c>
+      <c r="I47" s="3">
         <v>63940000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>65884000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>68419000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>72810000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>73061400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>73253400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>74850100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,8 +2692,11 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2641,8 +2748,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2694,8 +2804,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2747,8 +2860,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2800,47 +2916,50 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>640000</v>
+      </c>
+      <c r="E52" s="3">
         <v>632000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>681000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>755000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>320000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>759000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>981000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1343000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>954000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1004600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>892500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1076100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,8 +2972,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2906,47 +3028,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>330255000</v>
+      </c>
+      <c r="E54" s="3">
         <v>314534000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>326980000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>321464000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>314983000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>302970000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>316205000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>352641000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>375559000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>364372500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>366657400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>355242300</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3084,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2980,8 +3108,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3001,8 +3130,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3054,8 +3184,11 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3080,15 +3213,15 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>1601700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3107,47 +3240,50 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>294455000</v>
+        <v>307624000</v>
       </c>
       <c r="E59" s="3">
-        <v>309008000</v>
+        <v>290538000</v>
       </c>
       <c r="F59" s="3">
-        <v>303312000</v>
+        <v>304545000</v>
       </c>
       <c r="G59" s="3">
-        <v>296770000</v>
+        <v>297752000</v>
       </c>
       <c r="H59" s="3">
+        <v>291108000</v>
+      </c>
+      <c r="I59" s="3">
         <v>284311000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>297972000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>334931000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>357851000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>345753500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>348610300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>337134500</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3160,8 +3296,11 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3213,46 +3352,49 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2037000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2635000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2633000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2632000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2634000</v>
       </c>
       <c r="I61" s="3">
         <v>2634000</v>
       </c>
       <c r="J61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="K61" s="3">
         <v>2640000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2649000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>317700</v>
       </c>
       <c r="N61" s="3">
         <v>317700</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3266,8 +3408,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3319,8 +3464,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3372,8 +3520,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3425,8 +3576,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3478,47 +3632,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>320085000</v>
+      </c>
+      <c r="E66" s="3">
         <v>305056000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>318328000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>312826000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>306337000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>293996000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>306642000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>343067000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>365165000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>354114300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>356266900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>345258400</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,8 +3688,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3552,8 +3712,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3605,8 +3766,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3658,8 +3822,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3673,7 +3840,7 @@
         <v>533000</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -3711,8 +3878,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3764,47 +3934,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7038000</v>
+      </c>
+      <c r="E72" s="3">
         <v>8661000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5952000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4852000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6403000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9065000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7635000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4782000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2809000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2284600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2076800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2617900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3817,8 +3990,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3870,8 +4046,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3923,8 +4102,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3976,47 +4158,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9637000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8945000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8119000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8105000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8646000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8974000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9563000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9574000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10394000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10258200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10390500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9983900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4029,8 +4214,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4082,119 +4270,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1570000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2762000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1204000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-710000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-1150000</v>
+      </c>
+      <c r="I81" s="3">
         <v>1879000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3263000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2194000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>585000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>206000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-540000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2931500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>75700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-396600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1796700</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4214,8 +4411,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4267,8 +4465,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4320,8 +4521,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4373,8 +4577,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4426,8 +4633,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4479,8 +4689,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4532,61 +4745,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1634000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1129000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1086000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1461000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2265000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>845000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1236000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>860000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2166400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1429200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>803400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1344000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1329700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1045800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4606,8 +4825,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4659,8 +4879,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4712,8 +4935,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4765,61 +4991,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E94" s="3">
         <v>2119000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>78000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-146000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2817000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-202000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>44100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2079600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-629800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4839,38 +5071,39 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-51000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-50000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-51000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-35000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-49000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-50000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-52000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-50000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4892,8 +5125,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4945,8 +5181,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4998,8 +5237,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5051,61 +5293,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1801000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-842000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>538000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-624000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-582000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-78000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-484500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-290500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-129100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>530500</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5157,57 +5405,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E102" s="3">
         <v>662000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>322000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>75000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2586000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>49000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>148900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>947200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-38000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-446100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>570800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,255 +656,267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>939000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2561000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>464000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>2928000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6731000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2209000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1738000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1548000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>259500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5382200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>659600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>184100</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3">
         <v>4935200</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E9" s="3">
         <v>150000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>155000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>164000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>172000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>165000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>160000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>135000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>137000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>-232000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-188000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>-464700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>612600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>-504400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>-584300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>-876200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>838900</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>789000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2406000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>300000</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>2768000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6596000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2072000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1970000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1736000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>724200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4769600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1164000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>768400</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3">
         <v>4096300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -925,8 +937,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -981,8 +994,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1037,8 +1053,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1093,8 +1112,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1149,8 +1171,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1168,120 +1193,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-1250000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2812000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>-945000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>-1113000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1262000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>-511000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>408000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2531000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-412000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>959000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1317000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>763700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1915500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>756600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>635200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1255700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2961300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1873000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3506000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1577000</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>2520000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4200000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2621000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>779000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>231000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-504200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3466700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-97000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-451100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>1973900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1302,97 +1334,101 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>-47000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>45000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-54000</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>34000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-37000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-13000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>27000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-27600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>124800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-58800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-73000</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>-108000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1920000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3551000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1523000</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <v>2554000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4163000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2633000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>766000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1414,176 +1450,188 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E22" s="3">
         <v>35000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>49000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>58000</v>
       </c>
-      <c r="G22" s="3">
-        <v>43000</v>
-      </c>
       <c r="H22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="I22" s="3">
         <v>40000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>31400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>41800</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>903000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3502000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1465000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2525000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4139000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2613000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>748000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>252000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-538400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3585400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-163200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-531900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1824100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-395000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>712000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>245000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-558000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-385000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>657000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>845000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>388000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>87000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-54500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>585600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-273100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-157000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-457000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>33200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1638,120 +1686,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>802000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2790000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1220000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1868000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3294000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2225000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>661000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>268000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-483900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2999800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>109900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-374900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1790900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2762000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1204000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1879000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3263000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2194000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>585000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>206000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-540000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2931500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>75700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-396600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1796700</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1806,8 +1863,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1862,8 +1922,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1918,8 +1981,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1974,120 +2040,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>47000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-45000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>54000</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-34000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>37000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>13000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-27000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>27600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-124800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>58800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>73000</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>108000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1570000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2762000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1204000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1879000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3263000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2194000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>585000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>206000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-540000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2931500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>75700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-396600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1796700</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2142,125 +2217,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1570000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2762000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1204000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1879000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3263000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2194000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>585000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>206000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-540000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2931500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>75700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-396600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1796700</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2281,8 +2365,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2303,50 +2388,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2542000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2688000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2760000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2100000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1779000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4298000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5331000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5258000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2674000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2623000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2481800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1534600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1572600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2359,8 +2445,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2415,8 +2504,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2471,8 +2563,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2527,8 +2622,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2583,8 +2681,11 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2639,50 +2740,53 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68109000</v>
+      </c>
+      <c r="E47" s="3">
         <v>67351000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>67180000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>69488000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>71276000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>69762000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>63940000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>65884000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>68419000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>72810000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>73061400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>73253400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>74850100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,8 +2799,11 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2751,8 +2858,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2807,8 +2917,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2863,8 +2976,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2919,50 +3035,53 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>749000</v>
+      </c>
+      <c r="E52" s="3">
         <v>640000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>632000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>681000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>755000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>320000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>759000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>981000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1343000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>954000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1004600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>892500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1076100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2975,8 +3094,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3031,50 +3153,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>340280000</v>
+      </c>
+      <c r="E54" s="3">
         <v>330255000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>314534000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>326980000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>321464000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>314983000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>302970000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>316205000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>352641000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>375559000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>364372500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>366657400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>355242300</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3087,8 +3212,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3109,8 +3237,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3131,8 +3260,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3187,8 +3317,11 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3216,15 +3349,15 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>1601700</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,50 +3376,53 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>318411000</v>
+      </c>
+      <c r="E59" s="3">
         <v>307624000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>290538000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>304545000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>297752000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>291108000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>284311000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>297972000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>334931000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>357851000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>345753500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>348610300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>337134500</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3299,8 +3435,11 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3355,49 +3494,52 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2033000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2037000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2635000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2633000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2632000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2634000</v>
       </c>
       <c r="J61" s="3">
         <v>2634000</v>
       </c>
       <c r="K61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="L61" s="3">
         <v>2640000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2649000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="N61" s="3">
-        <v>317700</v>
       </c>
       <c r="O61" s="3">
         <v>317700</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3411,8 +3553,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3467,8 +3612,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3523,8 +3671,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3579,8 +3730,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3635,50 +3789,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>330111000</v>
+      </c>
+      <c r="E66" s="3">
         <v>320085000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>305056000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>318328000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>312826000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>306337000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>293996000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>306642000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>343067000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>365165000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>354114300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>356266900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>345258400</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3691,8 +3848,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3713,8 +3873,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3769,8 +3930,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3825,8 +3989,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3843,7 +4010,7 @@
         <v>533000</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -3881,8 +4048,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3937,50 +4107,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7766000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7038000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8661000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5952000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4852000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6403000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9065000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7635000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4782000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2809000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2284600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2076800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2617900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,8 +4166,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4049,8 +4225,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4105,8 +4284,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4161,50 +4343,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9636000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9637000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8945000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8119000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8105000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8646000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8974000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9563000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9574000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10394000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10258200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10390500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9983900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4402,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4273,125 +4461,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1570000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2762000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1204000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1879000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3263000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2194000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>585000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>206000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-540000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2931500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>75700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-396600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1796700</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4412,8 +4609,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4468,8 +4666,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4524,8 +4725,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4580,8 +4784,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4636,8 +4843,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4692,8 +4902,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4748,64 +4961,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1426000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1634000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1129000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1086000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1461000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2265000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>845000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1236000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>860000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2166400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1429200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>803400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1344000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1329700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1045800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4826,8 +5045,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4882,8 +5102,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4938,8 +5161,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4994,64 +5220,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2006000</v>
+      </c>
+      <c r="E94" s="3">
         <v>93000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2119000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>78000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-146000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2817000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-202000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>44100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2079600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-629800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5072,41 +5304,42 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-49000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-51000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-50000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-51000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-35000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-49000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-50000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-52000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-50000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5128,8 +5361,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5184,8 +5420,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5240,8 +5479,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5296,64 +5538,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>433000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-842000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>538000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-624000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-582000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-78000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-484500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-290500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-129100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>530500</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5408,60 +5656,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-74000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>662000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>322000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>75000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2586000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>49000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>148900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>947200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-38000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-446100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>570800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,267 +656,279 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>1256000</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>939000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2561000</v>
       </c>
-      <c r="G8" s="3">
-        <v>464000</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>434000</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>2928000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6731000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2209000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1738000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1548000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>259500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5382200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>659600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>184100</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3">
         <v>4935200</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E9" s="3">
         <v>130000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>150000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>155000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>164000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>172000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>165000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>160000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>135000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>137000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-232000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>-188000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>-464700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>612600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>-504400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>-584300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>-876200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>838900</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3">
+        <v>1147000</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>789000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2406000</v>
       </c>
-      <c r="G10" s="3">
-        <v>300000</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>270000</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>2768000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6596000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2072000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1970000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1736000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>724200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4769600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1164000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>768400</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3">
         <v>4096300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,8 +950,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -997,8 +1010,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1056,8 +1072,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1115,8 +1134,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1174,8 +1196,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1194,126 +1219,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>903000</v>
+      </c>
+      <c r="E17" s="3">
         <v>-1250000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2812000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>-945000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>-1113000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1262000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-511000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>408000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2531000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-412000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>959000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1317000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>763700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1915500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>756600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>635200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1255700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2961300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3">
+        <v>353000</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1873000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3506000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1577000</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+      <c r="H18" s="3">
+        <v>1547000</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>2520000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4200000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2621000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>779000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>231000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-504200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3466700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-97000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-451100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>1973900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1335,103 +1367,107 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-47000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>45000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-54000</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>34000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-37000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>27000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-27600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>124800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-58800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-73000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
         <v>-108000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="D21" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1920000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3551000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1523000</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+      <c r="H21" s="3">
+        <v>1493000</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>2554000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4163000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2633000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>766000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1453,185 +1489,197 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E22" s="3">
         <v>25000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>49000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>58000</v>
       </c>
       <c r="H22" s="3">
         <v>28000</v>
       </c>
       <c r="I22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="J22" s="3">
         <v>40000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>29000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>31400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>41800</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E23" s="3">
         <v>903000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3502000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1465000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2525000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4139000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2613000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>748000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>252000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-538400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3585400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-163200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-531900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1824100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E24" s="3">
         <v>101000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-395000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>712000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>245000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-558000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-385000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>657000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>845000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>388000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>87000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-16000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-54500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>585600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-273100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-157000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-457000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>33200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1689,126 +1737,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E26" s="3">
         <v>802000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2790000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1220000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1868000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3294000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2225000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>661000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>268000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-483900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2999800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>109900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-374900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1790900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E27" s="3">
         <v>784000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2762000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1204000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1879000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3263000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2194000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>585000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>206000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-540000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2931500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>75700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-396600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1796700</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1866,8 +1923,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1925,8 +1985,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1984,8 +2047,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2043,126 +2109,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>47000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-45000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>54000</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-34000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>37000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-27000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>27600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-124800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>58800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>73000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
         <v>108000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E33" s="3">
         <v>784000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1570000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2762000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1204000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1879000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3263000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2194000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>585000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>206000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-540000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2931500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>75700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-396600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1796700</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2220,131 +2295,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E35" s="3">
         <v>784000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1570000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2762000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1204000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1879000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3263000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2194000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>585000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>206000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-540000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2931500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>75700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-396600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1796700</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2366,8 +2450,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2389,53 +2474,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2542000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2688000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2760000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2100000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1779000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4298000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5331000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5258000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2674000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2623000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2481800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1534600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1572600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,8 +2534,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2507,8 +2596,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2566,8 +2658,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2625,8 +2720,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2684,8 +2782,11 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2743,53 +2844,56 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>69121000</v>
+      </c>
+      <c r="E47" s="3">
         <v>68109000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>67351000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>67180000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>69488000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>71276000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>69762000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>63940000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>65884000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>68419000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>72810000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>73061400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>73253400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>74850100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2802,8 +2906,11 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2861,8 +2968,11 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2920,8 +3030,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2979,8 +3092,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3038,53 +3154,56 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>768000</v>
+      </c>
+      <c r="E52" s="3">
         <v>749000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>640000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>632000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>681000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>755000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>320000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>759000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>981000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1343000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>954000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1004600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>892500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1076100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,8 +3216,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3156,53 +3278,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>337776000</v>
+      </c>
+      <c r="E54" s="3">
         <v>340280000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>330255000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>314534000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>326980000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>321464000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>314983000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>302970000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>316205000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>352641000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>375559000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>364372500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>366657400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>355242300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3215,8 +3340,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3238,8 +3366,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3261,8 +3390,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3320,8 +3450,11 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3352,15 +3485,15 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>1601700</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,53 +3512,56 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>315559000</v>
+      </c>
+      <c r="E59" s="3">
         <v>318411000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>307624000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>290538000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>304545000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>297752000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>291108000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>284311000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>297972000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>334931000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>357851000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>345753500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>348610300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>337134500</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3438,8 +3574,11 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3497,52 +3636,55 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2034000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2033000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2037000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2635000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2633000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2632000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2634000</v>
       </c>
       <c r="K61" s="3">
         <v>2634000</v>
       </c>
       <c r="L61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="M61" s="3">
         <v>2640000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2649000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="O61" s="3">
-        <v>317700</v>
       </c>
       <c r="P61" s="3">
         <v>317700</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -3556,8 +3698,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3615,8 +3760,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3674,8 +3822,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3733,8 +3884,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3792,53 +3946,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>327692000</v>
+      </c>
+      <c r="E66" s="3">
         <v>330111000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>320085000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>305056000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>318328000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>312826000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>306337000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>293996000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>306642000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>343067000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>365165000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>354114300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>356266900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>345258400</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3851,8 +4008,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3874,8 +4034,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3933,8 +4094,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3992,8 +4156,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4013,7 +4180,7 @@
         <v>533000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -4051,8 +4218,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4110,53 +4280,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7965000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7766000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7038000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8661000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5952000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4852000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6403000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9065000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7635000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4782000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2809000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2284600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2076800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2617900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4169,8 +4342,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4228,8 +4404,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4287,8 +4466,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4346,53 +4528,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9551000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9636000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9637000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8945000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8119000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8105000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8646000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8974000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9563000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9574000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10394000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10258200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10390500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9983900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4405,8 +4590,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4464,131 +4652,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E81" s="3">
         <v>784000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1570000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2762000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1204000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1879000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3263000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2194000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>585000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>206000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-540000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2931500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>75700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-396600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1796700</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4610,8 +4807,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4669,8 +4867,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4728,8 +4929,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4787,8 +4991,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4846,8 +5053,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4905,8 +5115,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4964,67 +5177,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1426000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1634000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1129000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1086000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1461000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2265000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>845000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1236000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>860000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2166400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1429200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>803400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1344000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1329700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1045800</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5046,8 +5265,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5105,8 +5325,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5164,8 +5387,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5223,67 +5449,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1914000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>93000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2119000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>78000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-146000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2817000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-202000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>44100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2079600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-629800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5305,44 +5537,45 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-54000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-49000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-51000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-50000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-51000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-35000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-49000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-50000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-52000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-50000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -5364,8 +5597,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5423,8 +5659,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5482,8 +5721,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5541,67 +5783,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-369000</v>
+      </c>
+      <c r="E100" s="3">
         <v>433000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-842000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>538000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-624000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-582000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-78000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-484500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-290500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-129100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>530500</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5659,63 +5907,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-805000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-147000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-74000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>662000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>322000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>75000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2586000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>49000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>148900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>947200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-38000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-446100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>570800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,279 +656,291 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1256000</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
-        <v>939000</v>
+        <v>2157000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1270000</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G8" s="3">
-        <v>2561000</v>
+        <v>892000</v>
       </c>
       <c r="H8" s="3">
-        <v>434000</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
+        <v>2585000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>380000</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>2928000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6731000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2209000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1738000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1548000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>259500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5382200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>659600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>184100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3">
         <v>4935200</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>109000</v>
+        <v>761000</v>
       </c>
       <c r="E9" s="3">
-        <v>130000</v>
+        <v>741000</v>
       </c>
       <c r="F9" s="3">
-        <v>150000</v>
+        <v>783000</v>
       </c>
       <c r="G9" s="3">
-        <v>155000</v>
+        <v>902000</v>
       </c>
       <c r="H9" s="3">
-        <v>164000</v>
+        <v>805000</v>
       </c>
       <c r="I9" s="3">
-        <v>172000</v>
+        <v>837000</v>
       </c>
       <c r="J9" s="3">
+        <v>820000</v>
+      </c>
+      <c r="K9" s="3">
         <v>165000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>160000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>135000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>137000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>-232000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>-188000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>-464700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>612600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>-504400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>-584300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>-876200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>838900</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1147000</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+        <v>1396000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>529000</v>
       </c>
       <c r="F10" s="3">
-        <v>789000</v>
+        <v>-1105000</v>
       </c>
       <c r="G10" s="3">
-        <v>2406000</v>
+        <v>-10000</v>
       </c>
       <c r="H10" s="3">
-        <v>270000</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
+        <v>1780000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-457000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-1584000</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>2768000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6596000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2072000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1970000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1736000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>724200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4769600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1164000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>768400</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3">
         <v>4096300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -951,8 +963,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1013,8 +1026,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1075,31 +1091,34 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1137,8 +1156,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1199,8 +1221,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1220,132 +1245,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>903000</v>
+        <v>1503000</v>
       </c>
       <c r="E17" s="3">
-        <v>-1250000</v>
+        <v>1419000</v>
       </c>
       <c r="F17" s="3">
-        <v>2812000</v>
+        <v>1468000</v>
       </c>
       <c r="G17" s="3">
-        <v>-945000</v>
+        <v>1589000</v>
       </c>
       <c r="H17" s="3">
-        <v>-1113000</v>
+        <v>1431000</v>
       </c>
       <c r="I17" s="3">
-        <v>1262000</v>
+        <v>1457000</v>
       </c>
       <c r="J17" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="K17" s="3">
         <v>-511000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>408000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2531000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-412000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>959000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1317000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>763700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1915500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>756600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>635200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1255700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2961300</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>353000</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+        <v>654000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-149000</v>
       </c>
       <c r="F18" s="3">
-        <v>-1873000</v>
+        <v>-1790000</v>
       </c>
       <c r="G18" s="3">
-        <v>3506000</v>
+        <v>-697000</v>
       </c>
       <c r="H18" s="3">
-        <v>1547000</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3">
+        <v>1154000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1077000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2200000</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>2520000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4200000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2621000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>779000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>231000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-504200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3466700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-97000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-451100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>1973900</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1368,109 +1400,113 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+        <v>1172000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-516000</v>
       </c>
       <c r="F20" s="3">
-        <v>-47000</v>
+        <v>-2718000</v>
       </c>
       <c r="G20" s="3">
-        <v>45000</v>
+        <v>1223000</v>
       </c>
       <c r="H20" s="3">
-        <v>-54000</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+        <v>-2376000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2570000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>34000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-37000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>27000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>124800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-58800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-73000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>-108000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>344000</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+        <v>-518000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>367000</v>
       </c>
       <c r="F21" s="3">
+        <v>928000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1920000</v>
       </c>
-      <c r="G21" s="3">
-        <v>3551000</v>
-      </c>
       <c r="H21" s="3">
+        <v>3530000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1493000</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="J21" s="3">
+        <v>-2026000</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>2554000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4163000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2633000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>766000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1492,22 +1528,25 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>26000</v>
+        <v>61000</v>
       </c>
       <c r="E22" s="3">
+        <v>49000</v>
+      </c>
+      <c r="F22" s="3">
         <v>25000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>49000</v>
       </c>
       <c r="H22" s="3">
         <v>28000</v>
@@ -1516,170 +1555,179 @@
         <v>28000</v>
       </c>
       <c r="J22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K22" s="3">
         <v>40000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>31400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>41800</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-579000</v>
+      </c>
+      <c r="E23" s="3">
         <v>318000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>903000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3502000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1465000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2525000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4139000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2613000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>748000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>252000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-538400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3585400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-163200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-531900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1824100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="E24" s="3">
         <v>36000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>101000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-395000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>712000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>245000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-558000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-385000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>657000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>845000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>388000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>87000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-16000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-54500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>585600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-273100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-157000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-457000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>33200</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1740,132 +1788,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-466000</v>
+      </c>
+      <c r="E26" s="3">
         <v>282000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>802000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2790000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1220000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1868000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3294000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2225000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>661000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>268000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-483900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2999800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>109900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-374900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1790900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-480000</v>
+      </c>
+      <c r="E27" s="3">
         <v>264000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>784000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2762000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1204000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1879000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3263000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2194000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>585000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>206000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-540000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2931500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>75700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-396600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1796700</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1926,8 +1983,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1988,8 +2048,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2050,8 +2113,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2112,132 +2178,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>9000</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+        <v>-1172000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>516000</v>
       </c>
       <c r="F32" s="3">
-        <v>47000</v>
+        <v>2718000</v>
       </c>
       <c r="G32" s="3">
-        <v>-45000</v>
+        <v>-1223000</v>
       </c>
       <c r="H32" s="3">
-        <v>54000</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+        <v>2376000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2570000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>174000</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-34000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>37000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-27000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>27600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-124800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>58800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>73000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>108000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>264000</v>
+        <v>-469000</v>
       </c>
       <c r="E33" s="3">
-        <v>784000</v>
+        <v>275000</v>
       </c>
       <c r="F33" s="3">
-        <v>-1570000</v>
+        <v>795000</v>
       </c>
       <c r="G33" s="3">
-        <v>2762000</v>
+        <v>-1559000</v>
       </c>
       <c r="H33" s="3">
-        <v>1204000</v>
+        <v>2773000</v>
       </c>
       <c r="I33" s="3">
+        <v>1217000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1879000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3263000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2194000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>585000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>206000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-540000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2931500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>75700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-396600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1796700</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2298,137 +2373,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>264000</v>
+        <v>-469000</v>
       </c>
       <c r="E35" s="3">
-        <v>784000</v>
+        <v>275000</v>
       </c>
       <c r="F35" s="3">
-        <v>-1570000</v>
+        <v>795000</v>
       </c>
       <c r="G35" s="3">
-        <v>2762000</v>
+        <v>-1559000</v>
       </c>
       <c r="H35" s="3">
-        <v>1204000</v>
+        <v>2773000</v>
       </c>
       <c r="I35" s="3">
+        <v>1217000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1879000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3263000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2194000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>585000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>206000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-540000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2931500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>75700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-396600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1796700</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2451,8 +2535,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2475,56 +2560,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3061000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1736000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2542000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2688000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2760000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2100000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1779000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4298000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5331000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5258000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2674000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2623000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2481800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1534600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1572600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2537,31 +2623,34 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>106000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2599,31 +2688,34 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2661,31 +2753,34 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2723,31 +2818,34 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>31542000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>33116000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>33405000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>33205000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>34619000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>34689000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>35061000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2785,31 +2883,34 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>34680000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>34931000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>36024000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>35969000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>37455000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>36898000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>36950000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2847,56 +2948,59 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>69121000</v>
+        <v>47832000</v>
       </c>
       <c r="E47" s="3">
-        <v>68109000</v>
+        <v>45464000</v>
       </c>
       <c r="F47" s="3">
-        <v>67351000</v>
+        <v>44795000</v>
       </c>
       <c r="G47" s="3">
-        <v>67180000</v>
+        <v>45101000</v>
       </c>
       <c r="H47" s="3">
-        <v>69488000</v>
+        <v>44820000</v>
       </c>
       <c r="I47" s="3">
-        <v>71276000</v>
+        <v>47663000</v>
       </c>
       <c r="J47" s="3">
+        <v>49584000</v>
+      </c>
+      <c r="K47" s="3">
         <v>69762000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>63940000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>65884000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>68419000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>72810000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>73061400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>73253400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>74850100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2909,31 +3013,34 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>24000</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2971,31 +3078,34 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>11986000</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>12066000</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>12173000</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>12302000</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>12447000</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>12599000</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>12760000</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3033,8 +3143,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3095,8 +3208,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3157,56 +3273,59 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>768000</v>
+        <v>236188000</v>
       </c>
       <c r="E52" s="3">
-        <v>749000</v>
+        <v>229979000</v>
       </c>
       <c r="F52" s="3">
-        <v>640000</v>
+        <v>231799000</v>
       </c>
       <c r="G52" s="3">
-        <v>632000</v>
+        <v>221257000</v>
       </c>
       <c r="H52" s="3">
-        <v>681000</v>
+        <v>204200000</v>
       </c>
       <c r="I52" s="3">
-        <v>755000</v>
+        <v>213946000</v>
       </c>
       <c r="J52" s="3">
+        <v>205647000</v>
+      </c>
+      <c r="K52" s="3">
         <v>320000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>759000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>981000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1343000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>954000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1004600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>892500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1076100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3338,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3281,56 +3403,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>345662000</v>
+      </c>
+      <c r="E54" s="3">
         <v>337776000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>340280000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>330255000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>314534000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>326980000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>321464000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>314983000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>302970000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>316205000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>352641000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>375559000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>364372500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>366657400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>355242300</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3343,8 +3468,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3367,8 +3495,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3391,31 +3520,32 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>18103000</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>18465000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>19244000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>19952000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>19973000</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>21170000</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>22254000</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -3453,31 +3583,34 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>907000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2476000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2008000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>979000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2518000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1870000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3488,15 +3621,15 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>1601700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3515,56 +3648,59 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>315559000</v>
+        <v>4846000</v>
       </c>
       <c r="E59" s="3">
-        <v>318411000</v>
+        <v>4727000</v>
       </c>
       <c r="F59" s="3">
-        <v>307624000</v>
+        <v>5035000</v>
       </c>
       <c r="G59" s="3">
-        <v>290538000</v>
+        <v>6643000</v>
       </c>
       <c r="H59" s="3">
-        <v>304545000</v>
+        <v>6564000</v>
       </c>
       <c r="I59" s="3">
-        <v>297752000</v>
+        <v>6536000</v>
       </c>
       <c r="J59" s="3">
+        <v>7467000</v>
+      </c>
+      <c r="K59" s="3">
         <v>291108000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>284311000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>297972000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>334931000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>357851000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>345753500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>348610300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>337134500</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3577,31 +3713,34 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>23856000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>25668000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>26287000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>27564000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>27516000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>30224000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>31591000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3639,55 +3778,58 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2034000</v>
+        <v>4399000</v>
       </c>
       <c r="E61" s="3">
-        <v>2033000</v>
+        <v>4075000</v>
       </c>
       <c r="F61" s="3">
-        <v>2037000</v>
+        <v>4101000</v>
       </c>
       <c r="G61" s="3">
+        <v>4048000</v>
+      </c>
+      <c r="H61" s="3">
+        <v>4046000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>4030000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>4050000</v>
+      </c>
+      <c r="K61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2633000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2632000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2635000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2634000</v>
       </c>
       <c r="L61" s="3">
         <v>2634000</v>
       </c>
       <c r="M61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="N61" s="3">
         <v>2640000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2649000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="P61" s="3">
-        <v>317700</v>
       </c>
       <c r="Q61" s="3">
         <v>317700</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -3701,31 +3843,34 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>306500000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>297749000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>299536000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>288309000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>272719000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>283303000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>276356000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3763,8 +3908,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3825,8 +3973,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3887,8 +4038,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3949,56 +4103,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>327692000</v>
+        <v>334755000</v>
       </c>
       <c r="E66" s="3">
-        <v>330111000</v>
+        <v>327492000</v>
       </c>
       <c r="F66" s="3">
-        <v>320085000</v>
+        <v>329924000</v>
       </c>
       <c r="G66" s="3">
-        <v>305056000</v>
+        <v>319921000</v>
       </c>
       <c r="H66" s="3">
-        <v>318328000</v>
+        <v>304281000</v>
       </c>
       <c r="I66" s="3">
-        <v>312826000</v>
+        <v>317557000</v>
       </c>
       <c r="J66" s="3">
+        <v>311997000</v>
+      </c>
+      <c r="K66" s="3">
         <v>306337000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>293996000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>306642000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>343067000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>365165000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>354114300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>356266900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>345258400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4011,8 +4168,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4035,8 +4195,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4097,8 +4258,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4159,8 +4323,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4183,7 +4350,7 @@
         <v>533000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -4221,8 +4388,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4283,56 +4453,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7431000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7965000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7766000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7038000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8661000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5952000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4852000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6403000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9065000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7635000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4782000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2809000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2284600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2076800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2617900</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4345,8 +4518,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4407,8 +4583,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4469,8 +4648,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4531,56 +4713,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10165000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9551000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9636000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9637000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8945000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8119000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8105000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8646000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8974000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9563000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9574000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10394000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10258200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10390500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9983900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4778,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4655,137 +4843,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>264000</v>
+        <v>-469000</v>
       </c>
       <c r="E81" s="3">
-        <v>784000</v>
+        <v>275000</v>
       </c>
       <c r="F81" s="3">
-        <v>-1570000</v>
+        <v>795000</v>
       </c>
       <c r="G81" s="3">
-        <v>2762000</v>
+        <v>-1559000</v>
       </c>
       <c r="H81" s="3">
-        <v>1204000</v>
+        <v>2773000</v>
       </c>
       <c r="I81" s="3">
+        <v>1217000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1879000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3263000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2194000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>585000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>206000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-540000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2931500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>75700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-396600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1796700</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4808,31 +5005,32 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4870,8 +5068,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4932,8 +5133,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4994,8 +5198,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5056,8 +5263,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5118,8 +5328,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5180,70 +5393,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1364000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1478000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1426000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1634000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1129000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1086000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1461000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2265000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>845000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1236000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>860000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2166400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1429200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>803400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1344000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1329700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1045800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5266,31 +5485,32 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5328,8 +5548,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5390,8 +5613,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5452,70 +5678,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-401000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>93000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2119000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>78000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-146000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2817000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-202000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>44100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2079600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-629800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5538,47 +5770,48 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-53000</v>
+        <v>53000</v>
       </c>
       <c r="E96" s="3">
-        <v>-54000</v>
+        <v>53000</v>
       </c>
       <c r="F96" s="3">
+        <v>54000</v>
+      </c>
+      <c r="G96" s="3">
+        <v>141000</v>
+      </c>
+      <c r="H96" s="3">
+        <v>51000</v>
+      </c>
+      <c r="I96" s="3">
+        <v>50000</v>
+      </c>
+      <c r="J96" s="3">
+        <v>51000</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-49000</v>
       </c>
-      <c r="G96" s="3">
-        <v>-51000</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="M96" s="3">
         <v>-50000</v>
       </c>
-      <c r="I96" s="3">
-        <v>-51000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-35000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-49000</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-50000</v>
       </c>
-      <c r="M96" s="3">
-        <v>-52000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-50000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -5600,8 +5833,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5662,8 +5898,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5724,8 +5963,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5786,93 +6028,99 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-369000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>433000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-842000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>538000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-624000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-582000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-78000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-484500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-290500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-129100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>530500</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5910,66 +6158,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1322000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-805000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-147000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-74000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>662000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>322000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>75000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2586000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>49000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>148900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>947200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-446100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>570800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,291 +656,303 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2157000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1270000</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
-        <v>892000</v>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
+        <v>882000</v>
+      </c>
+      <c r="I8" s="3">
         <v>2585000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>380000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>2928000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6731000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2209000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1738000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>259500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5382200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>659600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>184100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3">
         <v>4935200</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>847000</v>
+      </c>
+      <c r="E9" s="3">
         <v>761000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>741000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>783000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>902000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>805000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>837000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>820000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>165000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>160000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>135000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>137000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>-232000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>-188000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>-464700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>612600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>-504400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>-584300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>-876200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>838900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-602000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1396000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>529000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1105000</v>
       </c>
-      <c r="G10" s="3">
-        <v>-10000</v>
-      </c>
       <c r="H10" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1780000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-457000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1584000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>2768000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6596000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2072000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1970000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1736000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>724200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4769600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1164000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>768400</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3">
         <v>4096300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -964,8 +976,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1029,8 +1042,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1094,8 +1110,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1120,8 +1139,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1159,8 +1178,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1224,8 +1246,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1246,138 +1271,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1567000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1503000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1419000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1468000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1589000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1431000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1457000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1436000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-511000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>408000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2531000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-412000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>959000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1317000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>763700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1915500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>756600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>635200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1255700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2961300</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1322000</v>
+      </c>
+      <c r="E18" s="3">
         <v>654000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-149000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1790000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-697000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-707000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1154000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1077000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>2520000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4200000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2621000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>779000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>231000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-504200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3466700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-97000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-451100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>1973900</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1401,115 +1433,119 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1747000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1172000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-516000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2718000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1223000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2376000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2570000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-174000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-37000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>27000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-27600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>124800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-58800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-73000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
         <v>-108000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-518000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>367000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>928000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1920000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-1930000</v>
+      </c>
+      <c r="I21" s="3">
         <v>3530000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1493000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2026000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>2554000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4163000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2633000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>766000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1531,25 +1567,28 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E22" s="3">
         <v>61000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>49000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25000</v>
       </c>
-      <c r="G22" s="3">
-        <v>35000</v>
-      </c>
       <c r="H22" s="3">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="I22" s="3">
         <v>28000</v>
@@ -1558,176 +1597,185 @@
         <v>28000</v>
       </c>
       <c r="K22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="L22" s="3">
         <v>40000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>29000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>31400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>41800</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>380000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-579000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>318000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>903000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3502000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1465000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2525000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4139000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2613000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>748000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>252000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-538400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3585400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-163200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-531900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1824100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-113000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>36000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>101000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-395000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>712000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>245000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-558000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-385000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>657000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>845000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>388000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>87000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-54500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>585600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-273100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-157000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-457000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>33200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1791,138 +1839,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>358000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-466000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>282000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>802000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2790000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1220000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1868000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3294000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2225000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>661000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>268000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-483900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2999800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>109900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-374900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1790900</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-480000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>264000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>784000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2762000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1204000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1879000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3263000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2194000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>585000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>206000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-540000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2931500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>75700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-396600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1796700</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1986,8 +2043,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2051,8 +2111,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2116,8 +2179,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2181,138 +2247,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1747000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1172000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>516000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2718000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1223000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2376000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2570000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>174000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>37000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>27600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-124800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>58800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>73000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
         <v>108000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-469000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>275000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>795000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1559000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2773000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1217000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1879000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3263000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2194000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>585000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>206000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-540000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2931500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>75700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-396600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1796700</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2376,143 +2451,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-469000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>275000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>795000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1559000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2773000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1217000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1879000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3263000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2194000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>585000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>206000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-540000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2931500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>75700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-396600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1796700</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2536,8 +2620,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2561,59 +2646,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3767000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3061000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1736000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2542000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2688000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2760000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2100000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1779000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4298000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5331000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5258000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2674000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2623000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2481800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1534600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1572600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2626,35 +2712,38 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="3">
         <v>77000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>76000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>75000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>73000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>71000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>106000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>108000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2691,8 +2780,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2717,8 +2809,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2756,8 +2848,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2782,8 +2877,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2821,35 +2916,38 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31673000</v>
+      </c>
+      <c r="E45" s="3">
         <v>31542000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33116000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33405000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33205000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34619000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34689000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>35061000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2886,35 +2984,38 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35443000</v>
+      </c>
+      <c r="E46" s="3">
         <v>34680000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34931000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36024000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35969000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37455000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36898000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36950000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2951,59 +3052,62 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46037000</v>
+      </c>
+      <c r="E47" s="3">
         <v>47832000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45464000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>44795000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45101000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>44820000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>47663000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>49584000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>69762000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>63940000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>65884000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>68419000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>72810000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>73061400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>73253400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>74850100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3016,13 +3120,16 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>20000</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>3</v>
@@ -3030,20 +3137,20 @@
       <c r="F48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
         <v>24000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -3081,35 +3188,38 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11887000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11986000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12066000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12173000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12302000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12447000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12599000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12760000</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
@@ -3146,8 +3256,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3211,8 +3324,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3276,59 +3392,62 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>230269000</v>
+      </c>
+      <c r="E52" s="3">
         <v>236188000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>229979000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>231799000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>221257000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>204200000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>213946000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>205647000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>320000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>759000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>981000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1343000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>954000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1004600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>892500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1076100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,8 +3460,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3406,59 +3528,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>338450000</v>
+      </c>
+      <c r="E54" s="3">
         <v>345662000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>337776000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>340280000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>330255000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>314534000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>326980000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>321464000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>314983000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>302970000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>316205000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>352641000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>375559000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>364372500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>366657400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>355242300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3596,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3496,8 +3624,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3521,35 +3650,36 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16742000</v>
+      </c>
+      <c r="E57" s="3">
         <v>18103000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18465000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19244000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19952000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19973000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21170000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22254000</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -3586,35 +3716,38 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2439000</v>
+      </c>
+      <c r="E58" s="3">
         <v>907000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2476000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2008000</v>
       </c>
-      <c r="G58" s="3">
-        <v>410000</v>
-      </c>
       <c r="H58" s="3">
+        <v>401000</v>
+      </c>
+      <c r="I58" s="3">
         <v>979000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2518000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1870000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3624,15 +3757,15 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1601700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3651,59 +3784,62 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4108000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4846000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4727000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5035000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6643000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6564000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6536000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7467000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>291108000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>284311000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>297972000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>334931000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>357851000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>345753500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>348610300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>337134500</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3716,35 +3852,38 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23907000</v>
+      </c>
+      <c r="E60" s="3">
         <v>23856000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25668000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26287000</v>
       </c>
-      <c r="G60" s="3">
-        <v>27564000</v>
-      </c>
       <c r="H60" s="3">
+        <v>27555000</v>
+      </c>
+      <c r="I60" s="3">
         <v>27516000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30224000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31591000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3781,58 +3920,61 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4395000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4399000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4075000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4101000</v>
       </c>
-      <c r="G61" s="3">
-        <v>4048000</v>
-      </c>
       <c r="H61" s="3">
+        <v>4057000</v>
+      </c>
+      <c r="I61" s="3">
         <v>4046000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4030000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4050000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2634000</v>
       </c>
       <c r="M61" s="3">
         <v>2634000</v>
       </c>
       <c r="N61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="O61" s="3">
         <v>2640000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2649000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>317700</v>
       </c>
       <c r="R61" s="3">
         <v>317700</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -3846,35 +3988,38 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300166000</v>
+      </c>
+      <c r="E62" s="3">
         <v>306500000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>297749000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>299536000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>288309000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>272719000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>283303000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>276356000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3911,8 +4056,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3976,8 +4124,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4041,8 +4192,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4106,59 +4260,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>328468000</v>
+      </c>
+      <c r="E66" s="3">
         <v>334755000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>327492000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>329924000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>319921000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>304281000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>317557000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>311997000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>306337000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>293996000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>306642000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>343067000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>365165000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>354114300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>356266900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>345258400</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4171,8 +4328,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4196,8 +4356,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4261,8 +4422,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4326,8 +4490,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4353,7 +4520,7 @@
         <v>533000</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -4391,8 +4558,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4456,59 +4626,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7713000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7431000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7965000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7766000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7038000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8661000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5952000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4852000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6403000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9065000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7635000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4782000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2809000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2284600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2076800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2617900</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4521,8 +4694,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4586,8 +4762,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4651,8 +4830,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4716,59 +4898,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9231000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10165000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9551000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9636000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9637000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8945000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8119000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8105000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8646000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8974000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9563000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9574000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10394000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10258200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10390500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9983900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4781,8 +4966,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4846,143 +5034,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-469000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>275000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>795000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1559000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2773000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1217000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1879000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3263000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2194000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>585000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>206000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-540000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2931500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>75700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-396600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1796700</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5006,8 +5203,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5032,8 +5230,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -5071,8 +5269,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5136,8 +5337,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5201,8 +5405,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5266,8 +5473,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5331,8 +5541,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5396,73 +5609,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1525000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1364000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1478000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1426000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1634000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1129000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1086000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1461000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2265000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>845000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1236000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>860000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2166400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1429200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>803400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1344000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1329700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1045800</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5486,8 +5705,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5512,8 +5732,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5551,8 +5771,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5616,8 +5839,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5681,73 +5907,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2769000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-401000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>93000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2119000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>78000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-146000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2817000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-202000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>44100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2079600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-629800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5771,50 +6003,51 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>53000</v>
+        <v>51000</v>
       </c>
       <c r="E96" s="3">
         <v>53000</v>
       </c>
       <c r="F96" s="3">
+        <v>53000</v>
+      </c>
+      <c r="G96" s="3">
         <v>54000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>141000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>51000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>50000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>51000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-35000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-49000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-50000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-52000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-50000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -5836,8 +6069,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5901,8 +6137,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5966,8 +6205,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6031,73 +6273,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1950000</v>
+      </c>
+      <c r="E100" s="3">
         <v>359000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-369000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>433000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-842000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>538000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-624000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-582000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-78000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-484500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-290500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-129100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>530500</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6122,8 +6370,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6161,69 +6409,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>706000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1322000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-805000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-147000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-74000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>662000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>322000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>75000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2586000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>49000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>148900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>947200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-38000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-446100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>570800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,303 +656,315 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3750000</v>
+      </c>
+      <c r="E8" s="3">
         <v>245000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2157000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1270000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>882000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2585000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>380000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>2928000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6731000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2209000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1738000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1548000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>259500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5382200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>659600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>184100</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3">
         <v>4935200</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>819000</v>
+      </c>
+      <c r="E9" s="3">
         <v>847000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>761000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>741000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>783000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>902000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>805000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>837000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>820000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>165000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>160000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>135000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>137000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>-232000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>-188000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>-464700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>612600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>-504400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>-584300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>-876200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>838900</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2931000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-602000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1396000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>529000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1105000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-20000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1780000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-457000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-1584000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3">
         <v>2768000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6596000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2072000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1970000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1736000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>724200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4769600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1164000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>768400</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3">
         <v>4096300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -977,8 +989,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1045,8 +1058,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1113,8 +1129,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1142,8 +1161,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1181,8 +1200,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1249,8 +1271,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1272,144 +1297,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1496000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1567000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1503000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1419000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1468000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1589000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1431000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1457000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1436000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-511000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>408000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2531000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-412000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>959000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1317000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>763700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1915500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>756600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>635200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1255700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2961300</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2254000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1322000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>654000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-149000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1790000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-707000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1154000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1077000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2200000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>2520000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4200000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2621000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>779000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>231000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-504200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3466700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-97000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-451100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>1973900</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1434,121 +1466,125 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2246000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1747000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1172000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-516000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2718000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1223000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2376000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2570000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-174000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-37000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>27000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-27600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>124800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-58800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-73000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
         <v>-108000</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E21" s="3">
         <v>425000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-518000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>367000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>928000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1930000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3530000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1493000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2026000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>2554000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4163000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2633000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>766000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1570,28 +1606,31 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E22" s="3">
         <v>45000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>61000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>49000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>25000</v>
       </c>
       <c r="H22" s="3">
         <v>25000</v>
       </c>
       <c r="I22" s="3">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="J22" s="3">
         <v>28000</v>
@@ -1600,182 +1639,191 @@
         <v>28000</v>
       </c>
       <c r="L22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="M22" s="3">
         <v>40000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>29000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>31400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>41800</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E23" s="3">
         <v>380000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-579000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>318000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>903000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3502000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1465000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2525000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4139000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2613000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>748000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>252000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-538400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3585400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-163200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-531900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1824100</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>22000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-113000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>36000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>101000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-395000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>712000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>245000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-558000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-385000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>657000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>845000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>388000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>87000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-16000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-54500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>585600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-273100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-157000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-457000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>33200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1842,144 +1890,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E26" s="3">
         <v>358000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-466000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>282000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>802000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2790000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1220000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1868000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3294000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2225000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>661000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>268000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-483900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2999800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>109900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-374900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1790900</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E27" s="3">
         <v>334000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-480000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>264000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>784000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2762000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1204000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1879000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3263000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2194000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>585000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>206000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-540000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2931500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>75700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-396600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1796700</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2046,8 +2103,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2114,8 +2174,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2182,8 +2245,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2250,144 +2316,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2246000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1747000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1172000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>516000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2718000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1223000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2376000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2570000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>174000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>37000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-27000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>27600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-124800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>58800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>73000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
         <v>108000</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E33" s="3">
         <v>345000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-469000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>275000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>795000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1559000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2773000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1217000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1879000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3263000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2194000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>585000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>206000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-540000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2931500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>75700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-396600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1796700</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2454,149 +2529,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E35" s="3">
         <v>345000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-469000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>275000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>795000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1559000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2773000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1217000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1879000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3263000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2194000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>585000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>206000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-540000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2931500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>75700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-396600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1796700</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2621,8 +2705,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2647,62 +2732,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3887000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3767000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3061000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1736000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2542000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2688000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2760000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2100000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1779000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4298000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5331000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5258000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2674000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2623000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2481800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1534600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1572600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2715,38 +2801,41 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>77000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>76000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>75000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>73000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>71000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>106000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>108000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2783,8 +2872,11 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2812,8 +2904,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2851,8 +2943,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2880,8 +2975,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2919,38 +3014,41 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29504000</v>
+      </c>
+      <c r="E45" s="3">
         <v>31673000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31542000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33116000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33405000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33205000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34619000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34689000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35061000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2987,38 +3085,41 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33498000</v>
+      </c>
+      <c r="E46" s="3">
         <v>35443000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34680000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34931000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36024000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35969000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37455000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36898000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36950000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3055,62 +3156,65 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48375000</v>
+      </c>
+      <c r="E47" s="3">
         <v>46037000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47832000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45464000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44795000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>45101000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>44820000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47663000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>49584000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>69762000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>63940000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>65884000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>68419000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>72810000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>73061400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>73253400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>74850100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3123,37 +3227,40 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>20000</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>24000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -3191,38 +3298,41 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11770000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11887000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11986000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12066000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12173000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12302000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12447000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12599000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12760000</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
@@ -3259,8 +3369,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3327,8 +3440,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3395,62 +3511,65 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>218735000</v>
+      </c>
+      <c r="E52" s="3">
         <v>230269000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>236188000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>229979000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>231799000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>221257000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>204200000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>213946000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>205647000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>320000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>759000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>981000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1343000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>954000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1004600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>892500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1076100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,8 +3582,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3531,62 +3653,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>327193000</v>
+      </c>
+      <c r="E54" s="3">
         <v>338450000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>345662000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>337776000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>340280000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>330255000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>314534000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>326980000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>321464000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>314983000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>302970000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>316205000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>352641000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>375559000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>364372500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>366657400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>355242300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3599,8 +3724,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3625,8 +3753,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3651,38 +3780,39 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16275000</v>
+      </c>
+      <c r="E57" s="3">
         <v>16742000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18103000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18465000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19244000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19952000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19973000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21170000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22254000</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -3719,38 +3849,41 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1134000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2439000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>907000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2476000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2008000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>401000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>979000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2518000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1870000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3760,15 +3893,15 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>1601700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3787,62 +3920,65 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4622000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4108000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4846000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4727000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5035000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6643000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6564000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6536000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7467000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>291108000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>284311000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>297972000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>334931000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>357851000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>345753500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>348610300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>337134500</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3855,38 +3991,41 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22031000</v>
+      </c>
+      <c r="E60" s="3">
         <v>23907000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23856000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25668000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26287000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27555000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27516000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30224000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31591000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3923,61 +4062,64 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4333000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4395000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4399000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4075000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4101000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4057000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4046000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4030000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4050000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2634000</v>
       </c>
       <c r="N61" s="3">
         <v>2634000</v>
       </c>
       <c r="O61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="P61" s="3">
         <v>2640000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2649000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="R61" s="3">
-        <v>317700</v>
       </c>
       <c r="S61" s="3">
         <v>317700</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -3991,38 +4133,41 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>290304000</v>
+      </c>
+      <c r="E62" s="3">
         <v>300166000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>306500000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>297749000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>299536000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>288309000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>272719000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>283303000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>276356000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -4059,8 +4204,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4127,8 +4275,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4195,8 +4346,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4263,62 +4417,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>316668000</v>
+      </c>
+      <c r="E66" s="3">
         <v>328468000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>334755000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>327492000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>329924000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>319921000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>304281000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>317557000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>311997000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>306337000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>293996000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>306642000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>343067000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>365165000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>354114300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>356266900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>345258400</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4331,8 +4488,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4357,8 +4517,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4425,8 +4586,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4493,8 +4657,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4523,7 +4690,7 @@
         <v>533000</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -4561,8 +4728,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4629,62 +4799,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7623000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7713000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7431000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7965000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7766000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7038000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8661000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5952000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4852000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6403000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9065000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7635000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4782000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2809000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2284600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2076800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2617900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4697,8 +4870,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4765,8 +4941,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4833,8 +5012,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4901,62 +5083,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9768000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9231000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10165000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9551000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9636000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9637000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8945000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8119000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8105000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8646000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8974000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9563000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9574000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10394000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10258200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10390500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9983900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4969,8 +5154,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5037,149 +5225,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E81" s="3">
         <v>345000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-469000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>275000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>795000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1559000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2773000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1217000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1879000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3263000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2194000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>585000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>206000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-540000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2931500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>75700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-396600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1796700</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5204,8 +5401,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5233,8 +5431,8 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5272,8 +5470,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5340,8 +5541,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5408,8 +5612,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5476,8 +5683,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5544,8 +5754,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5612,76 +5825,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1594000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1525000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1364000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1478000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1426000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1634000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1129000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1086000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1461000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2265000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>845000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1236000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>860000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2166400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1429200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>803400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1344000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1329700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1045800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5706,8 +5925,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5735,8 +5955,8 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5774,8 +5994,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5842,8 +6065,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5910,76 +6136,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-953000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2769000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-401000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>93000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2119000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>78000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-146000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2817000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-202000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>44100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2079600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-629800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6004,53 +6236,54 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E96" s="3">
         <v>51000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>53000</v>
       </c>
       <c r="F96" s="3">
         <v>53000</v>
       </c>
       <c r="G96" s="3">
+        <v>53000</v>
+      </c>
+      <c r="H96" s="3">
         <v>54000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>141000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>51000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>50000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>51000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-35000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-49000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-50000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-52000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -6072,8 +6305,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6140,8 +6376,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6208,8 +6447,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6276,76 +6518,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-521000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1950000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>359000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-369000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>433000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-842000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>538000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-624000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-582000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-484500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-290500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-129100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>530500</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6373,8 +6621,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6412,72 +6660,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E102" s="3">
         <v>706000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1322000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-805000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-147000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-74000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>662000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>322000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>75000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2586000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>49000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>148900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>947200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-38000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-446100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>570800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,315 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>3750000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>245000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2157000</v>
       </c>
-      <c r="G8" s="3">
-        <v>1270000</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="H8" s="3">
+        <v>1247000</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>882000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2585000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>380000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3">
         <v>2928000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6731000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2209000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1738000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1548000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>259500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5382200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>659600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>184100</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3">
         <v>4935200</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>837000</v>
+      </c>
+      <c r="E9" s="3">
         <v>819000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>847000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>761000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>741000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>783000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>902000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>805000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>837000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>820000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>165000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>160000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>135000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>137000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>-232000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>-188000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>-464700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>612600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>-504400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>-584300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>-876200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>838900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1308000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2931000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-602000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1396000</v>
       </c>
-      <c r="G10" s="3">
-        <v>529000</v>
-      </c>
       <c r="H10" s="3">
+        <v>506000</v>
+      </c>
+      <c r="I10" s="3">
         <v>-1105000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-20000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1780000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-457000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1584000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3">
         <v>2768000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6596000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2072000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1970000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1736000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>724200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4769600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1164000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>768400</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3">
         <v>4096300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -990,8 +1002,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1061,8 +1074,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1132,8 +1148,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1164,8 +1183,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1203,8 +1222,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1274,8 +1296,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1298,150 +1323,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1518000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1496000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1567000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1503000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1419000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1468000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1589000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1431000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1457000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1436000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-511000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>408000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2531000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-412000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>959000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1317000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>763700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1915500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>756600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>635200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1255700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2961300</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1989000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2254000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1322000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>654000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-149000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1790000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-707000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1154000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1077000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2200000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>2520000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4200000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2621000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>779000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>231000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-504200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3466700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-97000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-451100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>1973900</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1467,127 +1499,131 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2203000</v>
+      </c>
+      <c r="E20" s="3">
         <v>2246000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1747000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1172000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-516000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2718000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1223000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2376000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2570000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-174000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>34000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-37000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>27000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-27600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>124800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-58800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-73000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-108000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>425000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-518000</v>
       </c>
-      <c r="G21" s="3">
-        <v>367000</v>
-      </c>
       <c r="H21" s="3">
+        <v>344000</v>
+      </c>
+      <c r="I21" s="3">
         <v>928000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1930000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3530000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1493000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2026000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>2554000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4163000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2633000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>766000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1609,8 +1645,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1618,22 +1657,22 @@
         <v>25000</v>
       </c>
       <c r="E22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F22" s="3">
         <v>45000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>61000</v>
       </c>
-      <c r="G22" s="3">
-        <v>49000</v>
-      </c>
       <c r="H22" s="3">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="I22" s="3">
         <v>25000</v>
       </c>
       <c r="J22" s="3">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="K22" s="3">
         <v>28000</v>
@@ -1642,188 +1681,197 @@
         <v>28000</v>
       </c>
       <c r="M22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="N22" s="3">
         <v>40000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>29000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>24000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>31400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>41800</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>380000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-579000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>318000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>903000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3502000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1465000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2525000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4139000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2613000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>748000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>252000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-538400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3585400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-163200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-531900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1824100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>22000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-113000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>36000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>101000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-395000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>712000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>245000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-558000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-385000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>657000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>845000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>388000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>87000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-16000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-54500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>585600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-273100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-157000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-457000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>33200</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1893,150 +1941,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>358000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-466000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>282000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>802000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2790000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1220000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1868000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3294000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2225000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>661000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>268000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-483900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2999800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>109900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-374900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1790900</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>334000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-480000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>264000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>784000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2762000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1204000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1879000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3263000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2194000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>585000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>206000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-540000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2931500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>75700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-396600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1796700</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2106,8 +2163,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2177,8 +2237,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2248,8 +2311,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2319,150 +2385,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2203000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2246000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1747000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1172000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>516000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2718000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1223000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2376000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2570000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>174000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>-34000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>37000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-27000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>27600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-124800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>58800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>73000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>108000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>345000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-469000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>275000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>795000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1559000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2773000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1217000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1879000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3263000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2194000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>585000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>206000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-540000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2931500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>75700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-396600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1796700</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2532,155 +2607,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>345000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-469000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>275000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>795000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1559000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2773000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1217000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1879000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3263000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2194000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>585000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>206000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-540000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2931500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>75700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-396600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1796700</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2706,8 +2790,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2733,65 +2818,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3784000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3887000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3767000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3061000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1736000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2542000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2688000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2760000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2100000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1779000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4298000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5331000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5258000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2674000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2623000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2481800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1534600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1572600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2804,41 +2890,44 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E42" s="3">
         <v>107000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>77000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>76000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>75000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>73000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>71000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>106000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>108000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2875,8 +2964,11 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2907,8 +2999,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2946,8 +3038,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2978,8 +3073,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3017,41 +3112,44 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30077000</v>
+      </c>
+      <c r="E45" s="3">
         <v>29504000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31673000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31542000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33116000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33405000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33205000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34619000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34689000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35061000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -3088,41 +3186,44 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33970000</v>
+      </c>
+      <c r="E46" s="3">
         <v>33498000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35443000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34680000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34931000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>36024000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35969000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37455000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36898000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36950000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3159,65 +3260,68 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>49851000</v>
+      </c>
+      <c r="E47" s="3">
         <v>48375000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46037000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>47832000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45464000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>44795000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45101000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44820000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>47663000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>49584000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>69762000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>63940000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>65884000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>68419000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>72810000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>73061400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>73253400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>74850100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3230,40 +3334,43 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>20000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>24000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3301,41 +3408,44 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11681000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11770000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11887000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11986000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12066000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12173000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12302000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12447000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12599000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12760000</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
@@ -3372,8 +3482,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3443,8 +3556,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3514,65 +3630,68 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>233381000</v>
+      </c>
+      <c r="E52" s="3">
         <v>218735000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>230269000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>236188000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>229979000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>231799000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>221257000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>204200000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>213946000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>205647000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>320000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>759000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>981000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1343000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>954000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1004600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>892500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1076100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,8 +3704,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3656,65 +3778,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>343722000</v>
+      </c>
+      <c r="E54" s="3">
         <v>327193000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>338450000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>345662000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>337776000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>340280000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>330255000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>314534000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>326980000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>321464000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>314983000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>302970000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>316205000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>352641000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>375559000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>364372500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>366657400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>355242300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,8 +3852,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3754,8 +3882,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3781,41 +3910,42 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15740000</v>
+      </c>
+      <c r="E57" s="3">
         <v>16275000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16742000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18103000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18465000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19244000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19952000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19973000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21170000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22254000</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -3852,41 +3982,44 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1134000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2439000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>907000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2476000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2008000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>401000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>979000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2518000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1870000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3896,15 +4029,15 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>1601700</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3923,65 +4056,68 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3958000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4622000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4108000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4846000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4727000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5035000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6643000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6564000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6536000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7467000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>291108000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>284311000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>297972000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>334931000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>357851000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>345753500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>348610300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>337134500</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,41 +4130,44 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20951000</v>
+      </c>
+      <c r="E60" s="3">
         <v>22031000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23907000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23856000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25668000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26287000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27555000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27516000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30224000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31591000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4065,64 +4204,67 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4669000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4333000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4395000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4399000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4075000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4101000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4057000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4046000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4030000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4050000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2634000</v>
       </c>
       <c r="O61" s="3">
         <v>2634000</v>
       </c>
       <c r="P61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2640000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2649000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="S61" s="3">
-        <v>317700</v>
       </c>
       <c r="T61" s="3">
         <v>317700</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -4136,41 +4278,44 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>307500000</v>
+      </c>
+      <c r="E62" s="3">
         <v>290304000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>300166000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>306500000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>297749000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>299536000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>288309000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>272719000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>283303000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>276356000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -4207,8 +4352,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4278,8 +4426,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4349,8 +4500,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4420,65 +4574,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>333120000</v>
+      </c>
+      <c r="E66" s="3">
         <v>316668000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>328468000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>334755000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>327492000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>329924000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>319921000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>304281000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>317557000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>311997000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>306337000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>293996000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>306642000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>343067000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>365165000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>354114300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>356266900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>345258400</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4491,8 +4648,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4518,8 +4678,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4589,8 +4750,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4660,8 +4824,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4693,7 +4860,7 @@
         <v>533000</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -4731,8 +4898,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4802,65 +4972,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7733000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7623000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7713000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7431000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7965000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7766000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7038000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8661000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5952000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4852000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6403000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9065000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7635000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4782000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2809000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2284600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2076800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2617900</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4873,8 +5046,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4944,8 +5120,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5015,8 +5194,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5086,65 +5268,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9821000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9768000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9231000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10165000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9551000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9636000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9637000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8945000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8119000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8105000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8646000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8974000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9563000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9574000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10394000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10258200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10390500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9983900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5157,8 +5342,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5228,155 +5416,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>345000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-469000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>275000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>795000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1559000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2773000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1217000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1879000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3263000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2194000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>585000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>206000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-540000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2931500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>75700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-396600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1796700</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5402,8 +5599,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5434,8 +5632,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5473,8 +5671,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5544,8 +5745,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5615,8 +5819,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5686,8 +5893,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5757,8 +5967,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5828,79 +6041,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1173000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1594000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1525000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1364000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1478000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1426000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1634000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1129000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1086000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1461000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2265000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>845000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1236000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>860000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2166400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1429200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>803400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1344000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1329700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1045800</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5926,8 +6145,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5958,8 +6178,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5997,8 +6217,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6068,8 +6291,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6139,79 +6365,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2765000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-953000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2769000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-401000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>93000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2119000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>78000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-146000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2817000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-202000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>44100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2079600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-629800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6237,56 +6469,57 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E96" s="3">
         <v>58000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>51000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>53000</v>
       </c>
       <c r="G96" s="3">
         <v>53000</v>
       </c>
       <c r="H96" s="3">
+        <v>53000</v>
+      </c>
+      <c r="I96" s="3">
         <v>54000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>141000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>51000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>50000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>51000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-35000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-49000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-50000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-50000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -6308,8 +6541,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6379,8 +6615,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6450,8 +6689,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6521,79 +6763,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1489000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-521000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1950000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>359000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-369000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>433000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-842000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>538000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-624000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-582000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-78000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-484500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-290500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-129100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>530500</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6624,8 +6872,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6663,75 +6911,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="E102" s="3">
         <v>120000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>706000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1322000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-805000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-147000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-74000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>662000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>322000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>75000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2586000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>49000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>148900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>947200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-38000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-446100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>570800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,339 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1435000</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>3750000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>245000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2157000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1270000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>882000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2585000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>380000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2928000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6731000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2209000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1738000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1548000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>259500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5382200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>659600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>184100</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="3">
         <v>4935200</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>808000</v>
+      </c>
+      <c r="E9" s="3">
         <v>831000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>837000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>819000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>847000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>761000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>741000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>783000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>902000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>805000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>837000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>820000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>165000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>160000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>135000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>137000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>-232000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>-188000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>-464700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>612600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>-504400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>-584300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>-876200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>838900</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1198000</v>
+      </c>
+      <c r="E10" s="3">
         <v>604000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1270000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2931000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-602000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1396000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>529000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1105000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-20000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1780000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-457000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1584000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>2768000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6596000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2072000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1970000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1736000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>724200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4769600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1164000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>768400</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3">
         <v>4096300</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1028,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1093,8 +1106,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1170,8 +1186,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1208,8 +1227,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1247,8 +1266,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1324,8 +1346,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1350,162 +1375,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1533000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1545000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1518000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1496000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1567000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1503000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1419000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1468000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1589000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1431000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1457000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1436000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-511000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>408000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2531000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-412000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>959000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1317000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>763700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1915500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>756600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>635200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1255700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2961300</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-110000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1951000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2254000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1322000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>654000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-149000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1790000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-707000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1154000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1077000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>2520000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4200000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2621000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>779000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>231000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-504200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3466700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-97000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-451100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>1973900</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1533,139 +1565,143 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>788000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-226000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2203000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2246000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1747000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1172000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-516000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2718000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1223000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2376000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2570000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-174000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>34000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-37000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>27000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-27600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>124800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-58800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-73000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-108000</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-315000</v>
+      </c>
+      <c r="E21" s="3">
         <v>116000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>252000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>425000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-518000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>367000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>928000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1930000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3530000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1493000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2026000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>2554000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4163000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2633000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>766000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1687,37 +1723,40 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E22" s="3">
         <v>44000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>63000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>45000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>61000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>49000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>25000</v>
       </c>
       <c r="K22" s="3">
         <v>25000</v>
       </c>
       <c r="L22" s="3">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="M22" s="3">
         <v>28000</v>
@@ -1726,200 +1765,209 @@
         <v>28000</v>
       </c>
       <c r="O22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="P22" s="3">
         <v>40000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>29000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>31400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>41800</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-358000</v>
+      </c>
+      <c r="E23" s="3">
         <v>72000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>189000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>380000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-579000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>318000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>903000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3502000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1465000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2525000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4139000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2613000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>748000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>252000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-538400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3585400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-163200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-531900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1824100</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-19000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-113000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>36000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>101000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-395000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>712000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>245000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-558000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-385000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>657000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>845000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>388000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>87000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-16000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-54500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>585600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-273100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-157000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-457000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>33200</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1995,162 +2043,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-186000</v>
+      </c>
+      <c r="E26" s="3">
         <v>91000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>185000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>358000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-466000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>282000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>802000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2790000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1220000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1868000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3294000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2225000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>661000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>268000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-483900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2999800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>109900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-374900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1790900</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-215000</v>
+      </c>
+      <c r="E27" s="3">
         <v>65000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>168000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>334000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-480000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>264000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>784000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2762000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1204000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1879000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3263000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2194000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>585000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>206000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-540000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2931500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>75700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-396600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1796700</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2226,8 +2283,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2303,8 +2363,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2380,8 +2443,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2457,162 +2523,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-788000</v>
+      </c>
+      <c r="E32" s="3">
         <v>226000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2203000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2246000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1747000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1172000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>516000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2718000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1223000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2376000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2570000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>174000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>37000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-27000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>27600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-124800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>58800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>73000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
         <v>108000</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="E33" s="3">
         <v>76000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>179000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>345000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-469000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>275000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>795000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1559000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2773000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1217000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1879000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3263000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2194000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>585000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>206000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-540000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2931500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>75700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-396600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1796700</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2688,167 +2763,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="E35" s="3">
         <v>76000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>179000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>345000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-469000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>275000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>795000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1559000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2773000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1217000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1879000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3263000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2194000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>585000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>206000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-540000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2931500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>75700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-396600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1796700</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2876,8 +2960,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2905,71 +2990,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5704000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4562000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3784000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3887000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3767000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3061000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1736000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2542000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2688000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2760000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2100000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1779000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4298000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5331000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5258000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2674000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2623000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2481800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1534600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1572600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2982,47 +3068,50 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>230000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>109000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>107000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>77000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>76000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>75000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>73000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>71000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>106000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>108000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -3059,8 +3148,11 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3097,8 +3189,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3136,8 +3228,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3174,8 +3269,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3213,47 +3308,50 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28585000</v>
+      </c>
+      <c r="E45" s="3">
         <v>29531000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30077000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29504000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31673000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31542000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33116000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33405000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33205000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34619000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34689000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35061000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -3290,47 +3388,50 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34289000</v>
+      </c>
+      <c r="E46" s="3">
         <v>34323000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>33970000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>33498000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35443000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>34680000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34931000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36024000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35969000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37455000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36898000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36950000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3367,71 +3468,74 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>53799000</v>
+      </c>
+      <c r="E47" s="3">
         <v>52453000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>49851000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48375000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>46037000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47832000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45464000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44795000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45101000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44820000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>47663000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>49584000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>69762000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>63940000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>65884000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>68419000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>72810000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>73061400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>73253400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>74850100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,13 +3548,16 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>54000</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>3</v>
@@ -3458,32 +3565,32 @@
       <c r="F48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
         <v>20000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
         <v>24000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -3521,47 +3628,50 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11660000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11654000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11681000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11770000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11887000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11986000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12066000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12173000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12302000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12447000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12599000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12760000</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
@@ -3598,8 +3708,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3675,8 +3788,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3752,71 +3868,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>237428000</v>
+      </c>
+      <c r="E52" s="3">
         <v>240148000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>233381000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>218735000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>230269000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>236188000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>229979000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>231799000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>221257000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>204200000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>213946000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>205647000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>320000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>759000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>981000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1343000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>954000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1004600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>892500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1076100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3829,8 +3948,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3906,71 +4028,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>352586000</v>
+      </c>
+      <c r="E54" s="3">
         <v>353558000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>343722000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>327193000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>338450000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>345662000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>337776000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>340280000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>330255000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>314534000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>326980000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>321464000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>314983000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>302970000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>316205000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>352641000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>375559000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>364372500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>366657400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>355242300</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3983,8 +4108,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4012,8 +4140,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4041,47 +4170,48 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14960000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15498000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15740000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16275000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16742000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18103000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18465000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19244000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19952000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19973000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>21170000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22254000</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -4118,47 +4248,50 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1047000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1032000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1253000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1134000</v>
       </c>
-      <c r="G58" s="3">
-        <v>2439000</v>
-      </c>
       <c r="H58" s="3">
+        <v>2431000</v>
+      </c>
+      <c r="I58" s="3">
         <v>907000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2476000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2008000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>401000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>979000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2518000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1870000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4168,15 +4301,15 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>1601700</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4195,71 +4328,74 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4069000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4024000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3958000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4622000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4108000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4846000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4727000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5035000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6643000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6564000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6536000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7467000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>291108000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>284311000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>297972000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>334931000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>357851000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>345753500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>348610300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>337134500</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4272,47 +4408,50 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20689000</v>
+      </c>
+      <c r="E60" s="3">
         <v>20554000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20951000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22031000</v>
       </c>
-      <c r="G60" s="3">
-        <v>23907000</v>
-      </c>
       <c r="H60" s="3">
+        <v>23899000</v>
+      </c>
+      <c r="I60" s="3">
         <v>23856000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25668000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26287000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27555000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27516000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30224000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31591000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4349,70 +4488,73 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4653000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4648000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4669000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4333000</v>
       </c>
-      <c r="G61" s="3">
-        <v>4395000</v>
-      </c>
       <c r="H61" s="3">
+        <v>4403000</v>
+      </c>
+      <c r="I61" s="3">
         <v>4399000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4075000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4101000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4057000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4046000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4030000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4050000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2634000</v>
       </c>
       <c r="Q61" s="3">
         <v>2634000</v>
       </c>
       <c r="R61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="S61" s="3">
         <v>2640000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2649000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="U61" s="3">
-        <v>317700</v>
       </c>
       <c r="V61" s="3">
         <v>317700</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -4426,47 +4568,50 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>316902000</v>
+      </c>
+      <c r="E62" s="3">
         <v>317855000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>307500000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>290304000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>300166000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>306500000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>297749000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>299536000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>288309000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>272719000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>283303000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>276356000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -4503,8 +4648,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4580,8 +4728,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4657,8 +4808,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4734,71 +4888,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>342244000</v>
+      </c>
+      <c r="E66" s="3">
         <v>343057000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>333120000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>316668000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>328468000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>334755000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>327492000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>329924000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>319921000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>304281000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>317557000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>311997000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>306337000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>293996000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>306642000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>343067000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>365165000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>354114300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>356266900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>345258400</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4811,8 +4968,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4840,8 +5000,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4917,8 +5078,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4994,8 +5158,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5033,7 +5200,7 @@
         <v>533000</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -5071,8 +5238,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5148,71 +5318,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7471000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7741000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7733000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7623000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7713000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7431000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7965000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7766000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7038000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8661000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5952000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4852000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6403000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9065000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7635000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4782000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2809000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2284600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2076800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2617900</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5225,8 +5398,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5302,8 +5478,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5379,8 +5558,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5456,71 +5638,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9420000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9696000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9821000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9768000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9231000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10165000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9551000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9636000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9637000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8945000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8119000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8105000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8646000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8974000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9563000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9574000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10394000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10258200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10390500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9983900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5533,8 +5718,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5610,167 +5798,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="E81" s="3">
         <v>76000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>179000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>345000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-469000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>275000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>795000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1559000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2773000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1217000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1879000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3263000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2194000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>585000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>206000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-540000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2931500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>75700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-396600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1796700</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5798,8 +5995,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5836,8 +6034,8 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -5875,8 +6073,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5952,8 +6153,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6029,8 +6233,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6106,8 +6313,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6183,8 +6393,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6260,85 +6473,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1621000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1370000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1173000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1594000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1525000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1364000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1478000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1426000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1634000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1129000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1086000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1461000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2265000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>845000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1236000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>860000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2166400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1429200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>803400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1344000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1329700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1045800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6366,8 +6585,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6404,8 +6624,8 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -6443,8 +6663,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6520,8 +6743,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6597,85 +6823,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1944000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2094000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2765000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-953000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2769000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-401000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>93000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2119000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>78000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-146000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2817000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-202000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>44100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>2079600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-629800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6703,8 +6935,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6712,53 +6945,53 @@
         <v>54000</v>
       </c>
       <c r="E96" s="3">
+        <v>54000</v>
+      </c>
+      <c r="F96" s="3">
         <v>57000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>58000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>51000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>53000</v>
       </c>
       <c r="I96" s="3">
         <v>53000</v>
       </c>
       <c r="J96" s="3">
+        <v>53000</v>
+      </c>
+      <c r="K96" s="3">
         <v>54000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>141000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>51000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>50000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>51000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-35000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-50000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-52000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-50000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -6780,8 +7013,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6857,8 +7093,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6934,8 +7173,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7011,85 +7253,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1465000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1502000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1489000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-521000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1950000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>359000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-369000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>433000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-842000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>538000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-624000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-582000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-78000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-484500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-290500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-129100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>530500</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7126,8 +7374,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7165,81 +7413,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1142000</v>
+      </c>
+      <c r="E102" s="3">
         <v>778000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-103000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>120000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>706000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1322000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-805000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-147000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-74000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>662000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>322000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>75000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2586000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>49000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>148900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>947200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-38000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-446100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>570800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>JXN</t>
   </si>
@@ -656,351 +656,363 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2902000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2006000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1435000</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>3750000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>245000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2157000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1270000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>882000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2585000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>380000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>2928000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6731000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2209000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1738000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1548000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>259500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5382200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>659600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>184100</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="3">
         <v>4935200</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>872000</v>
+      </c>
+      <c r="E9" s="3">
         <v>808000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>831000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>837000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>819000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>847000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>761000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>741000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>783000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>902000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>805000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>837000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>820000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>165000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>160000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>135000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>137000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>-232000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>-188000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>-464700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>612600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>-504400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>-584300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>-876200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>838900</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2030000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1198000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>604000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1270000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2931000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-602000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1396000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>529000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-1105000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-20000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1780000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-457000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1584000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>2768000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6596000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2072000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1970000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1736000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>724200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4769600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1164000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>768400</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3">
         <v>4096300</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,8 +1041,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1109,8 +1122,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1189,8 +1205,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1230,8 +1249,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1269,8 +1288,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1349,8 +1371,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1376,168 +1401,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1607000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1533000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1545000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1518000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1496000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1567000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1503000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1419000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1468000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1589000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1431000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1457000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1436000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-511000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>408000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2531000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-412000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>959000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1317000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>763700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1915500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>756600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>635200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1255700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2961300</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1295000</v>
+      </c>
+      <c r="E18" s="3">
         <v>473000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-110000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1951000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2254000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1322000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>654000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-149000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1790000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-707000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1154000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1077000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>2520000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4200000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2621000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>779000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>231000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-504200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3466700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-97000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-451100</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
         <v>1973900</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1566,145 +1598,149 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E20" s="3">
         <v>788000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-226000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2203000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2246000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1747000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1172000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-516000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2718000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1223000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2376000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2570000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-174000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>34000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-37000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>12000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-13000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>27000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-27600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>124800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-58800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-73000</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-108000</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-375000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-315000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>116000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>252000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>425000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-518000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>367000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>928000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1930000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3530000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1493000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2026000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>2554000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4163000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2633000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>766000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1726,40 +1762,43 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E22" s="3">
         <v>43000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>44000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>63000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>45000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>61000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>49000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>25000</v>
       </c>
       <c r="L22" s="3">
         <v>25000</v>
       </c>
       <c r="M22" s="3">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="N22" s="3">
         <v>28000</v>
@@ -1768,206 +1807,215 @@
         <v>28000</v>
       </c>
       <c r="P22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>40000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>29000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>31400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>41800</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-358000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>72000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>189000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>380000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-579000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>318000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>903000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1955000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3502000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1465000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2054000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1543000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2525000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4139000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2613000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>748000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>252000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-538400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3585400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-163200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-531900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3620000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1824100</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-172000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-19000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-113000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>36000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>101000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-395000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>712000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>245000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-558000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-385000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>657000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>845000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>388000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>87000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-16000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-54500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>585600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-273100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-157000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-457000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>33200</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2046,168 +2094,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-420000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-186000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>91000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>185000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>358000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-466000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>282000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>802000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1560000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2790000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1220000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1496000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1158000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1868000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3294000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2225000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>661000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>268000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-483900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2999800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>109900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-374900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3163000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1790900</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-435000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-215000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>65000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>168000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>334000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-480000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>264000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>784000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1570000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2762000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1204000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1497000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1150000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1879000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3263000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2194000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>585000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>206000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-540000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2931500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>75700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-396600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3109300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1796700</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2286,8 +2343,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2366,8 +2426,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2446,8 +2509,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2526,168 +2592,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1670000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-788000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>226000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2203000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2246000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1747000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1172000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>516000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2718000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1223000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2376000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2570000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>174000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-34000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>37000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-12000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>13000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-27000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>27600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-124800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>58800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>73000</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
         <v>108000</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-424000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-204000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>76000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>179000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>345000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-469000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>275000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>795000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1559000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2773000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1217000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1497000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1150000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1879000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3263000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2194000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>585000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>206000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-540000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2931500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>75700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-396600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3109300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1796700</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2766,173 +2841,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-424000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-204000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>76000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>179000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>345000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-469000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>275000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>795000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1559000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2773000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1217000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1497000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1150000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1879000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3263000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2194000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>585000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>206000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-540000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2931500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>75700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-396600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3109300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1796700</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2961,8 +3045,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2991,74 +3076,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5539000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5704000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4562000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3784000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3887000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3767000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3061000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1736000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2542000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2688000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2760000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2100000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1779000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4298000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5331000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5258000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2674000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2623000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2481800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1534600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1572600</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3071,8 +3157,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3080,41 +3169,41 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>230000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>109000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>107000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>77000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>76000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>75000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>73000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>71000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>106000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>108000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3151,8 +3240,11 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3192,8 +3284,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3231,8 +3323,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3272,8 +3367,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3311,50 +3406,53 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27085000</v>
+      </c>
+      <c r="E45" s="3">
         <v>28585000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29531000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30077000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29504000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31673000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31542000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33116000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33405000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33205000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34619000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34689000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35061000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3391,50 +3489,53 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32624000</v>
+      </c>
+      <c r="E46" s="3">
         <v>34289000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34323000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>33970000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33498000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35443000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34680000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>34931000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36024000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35969000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37455000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36898000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36950000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3471,74 +3572,77 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>55087000</v>
+      </c>
+      <c r="E47" s="3">
         <v>53799000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>52453000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>49851000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>48375000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46037000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>47832000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45464000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44795000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45101000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44820000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>47663000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>49584000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>69762000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>63940000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>65884000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>68419000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>72810000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>73061400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>73253400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>74850100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3551,49 +3655,52 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>54000</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>20000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
         <v>24000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -3631,50 +3738,53 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11634000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11660000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11654000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11681000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11770000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11887000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11986000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12066000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12173000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12302000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12447000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12599000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12760000</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
@@ -3711,8 +3821,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3791,8 +3904,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3871,74 +3987,77 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>224707000</v>
+      </c>
+      <c r="E52" s="3">
         <v>237428000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>240148000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>233381000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>218735000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>230269000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>236188000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>229979000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>231799000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>221257000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>204200000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>213946000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>205647000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>320000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>759000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>981000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1343000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>954000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1004600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>892500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1076100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3951,8 +4070,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4031,74 +4153,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>339537000</v>
+      </c>
+      <c r="E54" s="3">
         <v>352586000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>353558000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>343722000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>327193000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>338450000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>345662000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>337776000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>340280000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>330255000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>314534000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>326980000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>321464000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>314983000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>302970000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>316205000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>352641000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>375559000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>364372500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>366657400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>355242300</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4111,8 +4236,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4141,8 +4269,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4171,50 +4300,51 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14511000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14960000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15498000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15740000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16275000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16742000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18103000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18465000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19244000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19952000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19973000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>21170000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22254000</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -4251,50 +4381,53 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1047000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1032000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1253000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1134000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2431000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>907000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2476000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2008000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>401000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>979000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2518000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1870000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4304,15 +4437,15 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
         <v>1601700</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4331,74 +4464,77 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4552000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4069000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4024000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3958000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4622000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4108000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4846000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4727000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5035000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6643000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6564000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6536000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7467000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>291108000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>284311000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>297972000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>334931000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>357851000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>345753500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>348610300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>337134500</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,50 +4547,53 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19568000</v>
+      </c>
+      <c r="E60" s="3">
         <v>20689000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20554000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20951000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22031000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23899000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23856000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25668000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26287000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27555000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27516000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30224000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31591000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4491,73 +4630,76 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4570000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4653000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4648000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4669000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4333000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4403000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4399000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4075000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4101000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4057000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4046000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4030000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4050000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2635000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>2634000</v>
       </c>
       <c r="R61" s="3">
         <v>2634000</v>
       </c>
       <c r="S61" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="T61" s="3">
         <v>2640000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2649000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1068500</v>
-      </c>
-      <c r="V61" s="3">
-        <v>317700</v>
       </c>
       <c r="W61" s="3">
         <v>317700</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>317700</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -4571,50 +4713,53 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>305499000</v>
+      </c>
+      <c r="E62" s="3">
         <v>316902000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>317855000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>307500000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>290304000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>300166000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>306500000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>297749000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>299536000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>288309000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>272719000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>283303000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>276356000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -4651,8 +4796,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4731,8 +4879,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4811,8 +4962,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4891,74 +5045,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>329637000</v>
+      </c>
+      <c r="E66" s="3">
         <v>342244000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>343057000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>333120000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>316668000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>328468000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>334755000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>327492000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>329924000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>319921000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>304281000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>317557000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>311997000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>306337000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>293996000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>306642000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>343067000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>365165000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>354114300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>356266900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>345258400</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4971,8 +5128,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5001,8 +5161,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5081,8 +5242,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5161,8 +5325,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5203,7 +5370,7 @@
         <v>533000</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -5241,8 +5408,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5321,74 +5491,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6968000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7471000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7741000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7733000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7623000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7713000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7431000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7965000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7766000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7038000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8661000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5952000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4852000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6403000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9065000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7635000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4782000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2809000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2284600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2076800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2617900</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5401,8 +5574,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5481,8 +5657,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5561,8 +5740,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5641,74 +5823,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8963000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9420000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9696000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9821000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9768000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9231000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10165000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9551000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9636000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9637000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8945000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8119000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8105000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8646000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8974000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9563000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9574000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10394000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10258200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10390500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9983900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5721,8 +5906,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5801,173 +5989,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-424000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-204000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>76000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>179000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>345000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-469000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>275000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>795000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1559000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2773000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1217000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1497000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1150000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1879000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3263000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2194000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>585000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>206000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-540000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2931500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>75700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-396600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3109300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1796700</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5996,8 +6193,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6037,8 +6235,8 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -6076,8 +6274,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6156,8 +6357,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6236,8 +6440,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6316,8 +6523,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6396,8 +6606,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6476,88 +6689,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1045000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1621000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1370000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1173000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1594000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1525000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1364000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1478000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1426000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1634000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1129000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1086000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1461000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2265000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>845000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1236000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>860000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2166400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1429200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>803400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1344000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1329700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1045800</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6586,8 +6805,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6627,8 +6847,8 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -6666,8 +6886,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6746,8 +6969,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6826,88 +7052,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2430000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1944000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2094000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2765000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-953000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2769000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-401000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1914000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>93000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2119000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>78000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2882000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-146000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2817000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-202000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1920100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>44100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2079600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1499600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-629800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8939400</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6936,65 +7168,66 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>54000</v>
+        <v>64000</v>
       </c>
       <c r="E96" s="3">
         <v>54000</v>
       </c>
       <c r="F96" s="3">
+        <v>54000</v>
+      </c>
+      <c r="G96" s="3">
         <v>57000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>58000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>51000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>53000</v>
       </c>
       <c r="J96" s="3">
         <v>53000</v>
       </c>
       <c r="K96" s="3">
+        <v>53000</v>
+      </c>
+      <c r="L96" s="3">
         <v>54000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>141000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>51000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>50000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>51000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-49000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-50000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-52000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-50000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -7016,8 +7249,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7096,8 +7332,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7176,8 +7415,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7256,88 +7498,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1220000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1465000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1502000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1489000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-521000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1950000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>359000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-369000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>433000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1801000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-842000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1099000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>538000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-624000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-582000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-78000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-484500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-290500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-129100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>530500</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7377,8 +7625,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7416,84 +7664,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-165000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1142000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>778000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-103000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>120000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>706000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1322000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-805000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-147000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-74000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>662000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>322000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2520000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1040000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>75000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2586000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>49000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>148900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>947200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-38000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-446100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>570800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7363100</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
